--- a/geography_data.xlsx
+++ b/geography_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>鋸歯状（ギザギザ）, 溺れ谷, 養殖業（牡蠣・真珠）, 三陸海岸</t>
+          <t>V字谷が沈水してできたギザギザとした鋸歯状の海岸線。三陸海岸や志摩半島で見られ、静かな湾内では牡蠣や真珠の養殖が盛ん。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>石灰岩, 溶食（溶食作用）, ドリーネ, 秋吉台</t>
+          <t>石灰岩が二酸化炭素を含む雨水や地下水によって溶食されて形成された地形。山口県の秋吉台などが有名で、ドリーネや鍾乳洞が見られる。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>氷河侵食, U字谷, 溺れ谷, ノルウェー沿岸</t>
+          <t>氷河によって削られたU字谷が沈水して形成された、奥深く切り立った湾。ノルウェー沿岸やニュージーランド南島などに代表される。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大規模農場, 単一耕作（モノカルチャー）, 植民地主義, キャッシュクロップ</t>
+          <t>熱帯や亜熱帯地域の旧植民地を中心に、欧米の大資本と現地労働者を利用して単一産品（モノカルチャー）を大規模に栽培する農場形態。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -532,29 +532,6 @@
         </is>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>インフラマトリックス</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>都市インフラ, 整備状況, 産業基盤</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>人文地理</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
         <v>0</v>
       </c>
     </row>
